--- a/mfc_analysis.xlsx
+++ b/mfc_analysis.xlsx
@@ -418,66 +418,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1) 10*10 AC-1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2) 10*10 AC-2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3) 10*10 AC-3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4) 20*30 AC-1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5) 20*30 AC-2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6) 20*30 AC-3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7) 10*10 -1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8) 10*10 -2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>9) 10*10 -3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10) 20*30 -1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11) 20*30 -2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12) 20*30 -3</t>
         </is>
@@ -485,116 +485,1191 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.260638710951303</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09731196420334301</v>
+        <v>3.890663904835486</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3893297032518095</v>
+        <v>5.332447028046745</v>
       </c>
       <c r="D2" t="n">
-        <v>13.70286993495156</v>
+        <v>8.3363486816361</v>
       </c>
       <c r="E2" t="n">
-        <v>2.306325755042044</v>
+        <v>27.19133802799872</v>
       </c>
       <c r="F2" t="n">
-        <v>2.117518790521382</v>
+        <v>3.980667760579679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0021652110006705</v>
+        <v>7.007787388593213</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0004418900528879999</v>
+        <v>6.808509745971002</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0073734150744975</v>
+        <v>3.98837304763217</v>
       </c>
       <c r="J2" t="n">
-        <v>0.031999068683978</v>
+        <v>4.510286813981585</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0024586043730705</v>
+        <v>5.302369489447208</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004556987088815499</v>
+        <v>4.841858928615931</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5.003094356593673</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.048947816659028</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004648260056417001</v>
+        <v>0.5851082300767725</v>
       </c>
       <c r="C3" t="n">
-        <v>0.034711654289813</v>
+        <v>0.522986258174307</v>
       </c>
       <c r="D3" t="n">
-        <v>6.085532255081462</v>
+        <v>1.628491080742005</v>
       </c>
       <c r="E3" t="n">
-        <v>1.347240119686107</v>
+        <v>14.55054594658631</v>
       </c>
       <c r="F3" t="n">
-        <v>0.664602629733908</v>
+        <v>1.815771392128835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000627368038052</v>
+        <v>1.817378826767903</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.361805014257525</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000551772426948</v>
+        <v>0.298809985701501</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000352390773827</v>
+        <v>0.2285273091542455</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000488314425308</v>
+        <v>0.4469919294658825</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000488744874215</v>
+        <v>0.2937149883038715</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.095801731941006</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.659920605166074</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.204596264734023</v>
+        <v>0.260638710951303</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5855254111307195</v>
+        <v>0.09731196420334301</v>
       </c>
       <c r="D4" t="n">
-        <v>10.14453894622136</v>
+        <v>0.3893297032518095</v>
       </c>
       <c r="E4" t="n">
-        <v>3.214778345865951</v>
+        <v>13.70286993495156</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9700192359956606</v>
+        <v>2.306325755042044</v>
       </c>
       <c r="G4" t="n">
-        <v>0.152262618452185</v>
+        <v>2.117518790521382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.156759343098821</v>
+        <v>0.0021652110006705</v>
       </c>
       <c r="I4" t="n">
-        <v>0.477664533075141</v>
+        <v>0.0004418900528879999</v>
       </c>
       <c r="J4" t="n">
-        <v>1.600842948495223</v>
+        <v>0.0073734150744975</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7443027511563615</v>
+        <v>0.031999068683978</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9995937469720866</v>
+        <v>0.0024586043730705</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.004556987088815499</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.048947816659028</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.004648260056417001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.034711654289813</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.085532255081462</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.347240119686107</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.664602629733908</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.000627368038052</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.000551772426948</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000352390773827</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.000488314425308</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000488744874215</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.045993380402607</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.204687378449815</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8080011344865725</v>
+      </c>
+      <c r="E6" t="n">
+        <v>51.72984057647209</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21.63439983035576</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.652305474301149</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.157717785896153</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.157394053829013</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.481958253158266</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.603599138397931</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7485657653540785</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.006510951642859</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.665388135779145</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.518854781563277</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.99706583564569</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.013585289744186</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.022256030910453</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.263362301747604</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11.82173081162955</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7.380569138275961</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.200401631762891</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.86541852564851</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.781638704327011</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.413797233290427</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0124808695138</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.43463129332563</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.09538661069743</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.27714976796312</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.55887484249423</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.16173581400742</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.00165366586498</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0004109761474299999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0018805827357</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.43890317321478</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.03881335955613</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.14887510596162</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1606427591904477</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1775870890162063</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.172063174134683</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6784972261221696</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.92301052691643</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.07338544773530567</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3201887628718634</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4555328540189433</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.08714893936620234</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7188606512380955</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6049356084898563</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3945908661842886</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00355697972412</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.03413854733470834</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01289553244346833</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.09880297627915666</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2973194903816933</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001948832290898333</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00038016656725</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001948625022228333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.003632926943235</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.029602211323555</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.04209212793743</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.03794424977679</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.021004995401308</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.07446889531018799</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.03068339992672</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.09588876927506501</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.33784495508178</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.002134864826328</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.006104564594228</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.009442108102221999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.021438866457845</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.053644923741467</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.08228489058841501</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.059466203894242</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.052397894942304</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1176971565812468</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05090426093836399</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.03931603696488084</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3264530183247375</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.003153927925016833</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.04010854375467734</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.04572005648168934</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.04045685336146083</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1160553016736235</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.133827451930226</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.04787044327800601</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2735877314905575</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3681409620187374</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3279726585239908</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2712495554611014</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.444137259362102</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2210626653534808</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.386251195111474</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.359657034838904</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2514919473496493</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8510845062505394</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3312317525823848</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01945857821825933</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3485677713809064</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3242082840094785</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3637281572441885</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.290871236910972</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5372176069143202</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.06229335631010652</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.616367479082709</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4398154507876825</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4382681068536666</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7390509803329638</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7067976187477265</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2658653411554125</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7.523717734710464</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.816611486447833</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8.983677968210131</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.26405753940046</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.531445148924494</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18.62201254555251</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.992111378803024</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.656983389790216</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.185370095202316</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10.54428499526229</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.950760689767215</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5.290653599663878</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.380999465446317</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.245567603584957</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.175051320612</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.491549358021196</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.83963120378955</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.776610338665195</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6976452212868467</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.631070693293961</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.520268584221431</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.834561416475716</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6.313010970010249</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.579777674972076</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.112274693190759</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.140137497224204</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33.17418052703683</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.355795361524715</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.46982606003588</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.654707561261927</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1861410824993486</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.563701537848225</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.207795831910219</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.325600445405628</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.336838391767838</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.08882844182708</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.02925513073571033</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1098183653277503</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13.02127312430544</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.079951593225298</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.523201289168773</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.007762815402541999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05630109198308033</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.005135037539485333</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.014519680203295</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.048991589750928</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.006121654763870333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.04425198559360249</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.006830392033629167</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.08598110176079002</v>
+      </c>
+      <c r="E19" t="n">
+        <v>83.20003199243227</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12.31604279172807</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.389338030979408</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1328153497920892</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3000763822922767</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2030814130950392</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2213771794642667</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.027980503052396</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.006677028475722501</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.269322016905766</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2821455570464</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.017183352473826</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.001704823024636</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.177984933359486</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.22579834338467</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.036380446460234</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.000665287070856</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.000136663478564</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.162254285698864</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.00016097066329</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.008688304060566001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4811978167393967</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4900363563877667</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.04387573326828217</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.271907909393662</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1873097542707922</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1921104778511187</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7178758075196695</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.02452842996172199</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.34808707332193</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5769279933344955</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1476707220971022</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0494236670342955</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.243517474458036</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.435391632054803</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.359052708355061</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8.179711768762118</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.551616042213066</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.003040957913393</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.559203140993816</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9838916551834279</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.460050790882279</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.398553863684211</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.698154482592636</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.402463794527815</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.58817109840036</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6390745410579601</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.685456064040565</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.127550494823865</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.178046815611585</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.235215440311187</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.20010231146434</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.330567425580765</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.156959970210365</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.208415682338785</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.512317357308865</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.62122252732936</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.137822607243975</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.529468746913575</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.18517123499838</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.178068960384655</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.3931771063832999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.47120418466628</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.08776093735429501</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.15308647445388</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4156521769722</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.10725785190738</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.23133123273522</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.241312256688255</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.09858744833459999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.111486367107525</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.07202672100389999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.478646129744025</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.105825786358725</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.6899212798307999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.04349234923680001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0198749638569</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.062259830905425</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.058791909552</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.122030925043425</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.046791148354125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0297932096193</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.053363350850025</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.004982872281</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.405332007994125</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.102169506565425</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.69068752359285</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.002986863374625</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.000502558443825</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0015720055128</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.004929938005725</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.004052604187725</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.016245737253</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.39179711513152</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.80943880021522</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.68168553366058</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.51139678743243</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.37532346068617</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.505274571263333</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.41727041327995</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.11284519092067</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.2052877839372</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.5857436113086699</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.7839458690070301</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.64073586998868</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.002908857585145</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.00019540736982</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.00097073483092</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.41038345515838</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1024459098757</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.368814363456972</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.005298529783105</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0001469454712</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.00245459383032</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.006831306683905</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.00444109429162</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.02029170101992</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.00830510104125</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.016253335989</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.02147260099485</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.59268902657435</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3361130729916</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.746175823699545</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.04647126757815</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0066813929094</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.03796208530605</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.04557038270205</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.069198371892</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.06792448047855</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0001964876682</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.003852101268449999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.00670639377645</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.11671069172805</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.02031976799175</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.00295050864612</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01219356026055</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.00049201514985</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.00351114996855</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.0062420538777</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0054481884984</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.0108485963544</v>
       </c>
     </row>
   </sheetData>
@@ -608,66 +1683,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1) 10*10 AC-1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2) 10*10 AC-2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3) 10*10 AC-3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4) 20*30 AC-1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5) 20*30 AC-2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6) 20*30 AC-3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7) 10*10 -1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8) 10*10 -2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>9) 10*10 -3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10) 20*30 -1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11) 20*30 -2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12) 20*30 -3</t>
         </is>
@@ -675,7 +1750,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -708,6 +1783,9 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -748,10 +1826,13 @@
       <c r="L3" t="n">
         <v>1</v>
       </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -785,6 +1866,1075 @@
       </c>
       <c r="L4" t="n">
         <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -798,66 +2948,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1) 10*10 AC-1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2) 10*10 AC-2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3) 10*10 AC-3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4) 20*30 AC-1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5) 20*30 AC-2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6) 20*30 AC-3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7) 10*10 -1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8) 10*10 -2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>9) 10*10 -3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10) 20*30 -1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11) 20*30 -2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12) 20*30 -3</t>
         </is>
@@ -865,116 +3015,1191 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="C2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="F2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="G2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="H2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="I2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="J2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="K2" t="n">
-        <v>101</v>
+        <v>839</v>
       </c>
       <c r="L2" t="n">
-        <v>101</v>
+        <v>839</v>
+      </c>
+      <c r="M2" t="n">
+        <v>839</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="G3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="H3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="J3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="K3" t="n">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>180</v>
+      </c>
+      <c r="M3" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" t="n">
+        <v>101</v>
+      </c>
+      <c r="D4" t="n">
+        <v>101</v>
+      </c>
+      <c r="E4" t="n">
+        <v>101</v>
+      </c>
+      <c r="F4" t="n">
+        <v>101</v>
+      </c>
+      <c r="G4" t="n">
+        <v>101</v>
+      </c>
+      <c r="H4" t="n">
+        <v>101</v>
+      </c>
+      <c r="I4" t="n">
+        <v>101</v>
+      </c>
+      <c r="J4" t="n">
+        <v>101</v>
+      </c>
+      <c r="K4" t="n">
+        <v>101</v>
+      </c>
+      <c r="L4" t="n">
+        <v>101</v>
+      </c>
+      <c r="M4" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C5" t="n">
+        <v>47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>47</v>
+      </c>
+      <c r="E5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47</v>
+      </c>
+      <c r="H5" t="n">
+        <v>47</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47</v>
+      </c>
+      <c r="J5" t="n">
+        <v>47</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47</v>
+      </c>
+      <c r="L5" t="n">
+        <v>47</v>
+      </c>
+      <c r="M5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>360</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C6" t="n">
         <v>360</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D6" t="n">
         <v>360</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E6" t="n">
         <v>360</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F6" t="n">
         <v>360</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G6" t="n">
         <v>360</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H6" t="n">
         <v>360</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I6" t="n">
         <v>360</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J6" t="n">
         <v>360</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K6" t="n">
         <v>360</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
         <v>360</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M6" t="n">
         <v>360</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>900</v>
+      </c>
+      <c r="C7" t="n">
+        <v>900</v>
+      </c>
+      <c r="D7" t="n">
+        <v>900</v>
+      </c>
+      <c r="E7" t="n">
+        <v>900</v>
+      </c>
+      <c r="F7" t="n">
+        <v>900</v>
+      </c>
+      <c r="G7" t="n">
+        <v>900</v>
+      </c>
+      <c r="H7" t="n">
+        <v>900</v>
+      </c>
+      <c r="I7" t="n">
+        <v>900</v>
+      </c>
+      <c r="J7" t="n">
+        <v>900</v>
+      </c>
+      <c r="K7" t="n">
+        <v>900</v>
+      </c>
+      <c r="L7" t="n">
+        <v>900</v>
+      </c>
+      <c r="M7" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101</v>
+      </c>
+      <c r="C8" t="n">
+        <v>101</v>
+      </c>
+      <c r="D8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E8" t="n">
+        <v>101</v>
+      </c>
+      <c r="F8" t="n">
+        <v>101</v>
+      </c>
+      <c r="G8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H8" t="n">
+        <v>101</v>
+      </c>
+      <c r="I8" t="n">
+        <v>101</v>
+      </c>
+      <c r="J8" t="n">
+        <v>101</v>
+      </c>
+      <c r="K8" t="n">
+        <v>101</v>
+      </c>
+      <c r="L8" t="n">
+        <v>101</v>
+      </c>
+      <c r="M8" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>360</v>
+      </c>
+      <c r="C9" t="n">
+        <v>360</v>
+      </c>
+      <c r="D9" t="n">
+        <v>360</v>
+      </c>
+      <c r="E9" t="n">
+        <v>360</v>
+      </c>
+      <c r="F9" t="n">
+        <v>360</v>
+      </c>
+      <c r="G9" t="n">
+        <v>360</v>
+      </c>
+      <c r="H9" t="n">
+        <v>360</v>
+      </c>
+      <c r="I9" t="n">
+        <v>360</v>
+      </c>
+      <c r="J9" t="n">
+        <v>360</v>
+      </c>
+      <c r="K9" t="n">
+        <v>360</v>
+      </c>
+      <c r="L9" t="n">
+        <v>360</v>
+      </c>
+      <c r="M9" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>185</v>
+      </c>
+      <c r="C10" t="n">
+        <v>185</v>
+      </c>
+      <c r="D10" t="n">
+        <v>185</v>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="n">
+        <v>185</v>
+      </c>
+      <c r="G10" t="n">
+        <v>185</v>
+      </c>
+      <c r="H10" t="n">
+        <v>185</v>
+      </c>
+      <c r="I10" t="n">
+        <v>185</v>
+      </c>
+      <c r="J10" t="n">
+        <v>185</v>
+      </c>
+      <c r="K10" t="n">
+        <v>185</v>
+      </c>
+      <c r="L10" t="n">
+        <v>185</v>
+      </c>
+      <c r="M10" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79</v>
+      </c>
+      <c r="C11" t="n">
+        <v>79</v>
+      </c>
+      <c r="D11" t="n">
+        <v>79</v>
+      </c>
+      <c r="E11" t="n">
+        <v>79</v>
+      </c>
+      <c r="F11" t="n">
+        <v>79</v>
+      </c>
+      <c r="G11" t="n">
+        <v>79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>79</v>
+      </c>
+      <c r="I11" t="n">
+        <v>79</v>
+      </c>
+      <c r="J11" t="n">
+        <v>79</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79</v>
+      </c>
+      <c r="L11" t="n">
+        <v>79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>270</v>
+      </c>
+      <c r="C13" t="n">
+        <v>270</v>
+      </c>
+      <c r="D13" t="n">
+        <v>270</v>
+      </c>
+      <c r="E13" t="n">
+        <v>270</v>
+      </c>
+      <c r="F13" t="n">
+        <v>270</v>
+      </c>
+      <c r="G13" t="n">
+        <v>270</v>
+      </c>
+      <c r="H13" t="n">
+        <v>270</v>
+      </c>
+      <c r="I13" t="n">
+        <v>270</v>
+      </c>
+      <c r="J13" t="n">
+        <v>270</v>
+      </c>
+      <c r="K13" t="n">
+        <v>270</v>
+      </c>
+      <c r="L13" t="n">
+        <v>270</v>
+      </c>
+      <c r="M13" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>900</v>
+      </c>
+      <c r="C14" t="n">
+        <v>900</v>
+      </c>
+      <c r="D14" t="n">
+        <v>900</v>
+      </c>
+      <c r="E14" t="n">
+        <v>900</v>
+      </c>
+      <c r="F14" t="n">
+        <v>900</v>
+      </c>
+      <c r="G14" t="n">
+        <v>900</v>
+      </c>
+      <c r="H14" t="n">
+        <v>900</v>
+      </c>
+      <c r="I14" t="n">
+        <v>900</v>
+      </c>
+      <c r="J14" t="n">
+        <v>900</v>
+      </c>
+      <c r="K14" t="n">
+        <v>900</v>
+      </c>
+      <c r="L14" t="n">
+        <v>900</v>
+      </c>
+      <c r="M14" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>801</v>
+      </c>
+      <c r="C15" t="n">
+        <v>801</v>
+      </c>
+      <c r="D15" t="n">
+        <v>801</v>
+      </c>
+      <c r="E15" t="n">
+        <v>801</v>
+      </c>
+      <c r="F15" t="n">
+        <v>801</v>
+      </c>
+      <c r="G15" t="n">
+        <v>801</v>
+      </c>
+      <c r="H15" t="n">
+        <v>801</v>
+      </c>
+      <c r="I15" t="n">
+        <v>801</v>
+      </c>
+      <c r="J15" t="n">
+        <v>801</v>
+      </c>
+      <c r="K15" t="n">
+        <v>801</v>
+      </c>
+      <c r="L15" t="n">
+        <v>801</v>
+      </c>
+      <c r="M15" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>785</v>
+      </c>
+      <c r="C16" t="n">
+        <v>785</v>
+      </c>
+      <c r="D16" t="n">
+        <v>785</v>
+      </c>
+      <c r="E16" t="n">
+        <v>785</v>
+      </c>
+      <c r="F16" t="n">
+        <v>785</v>
+      </c>
+      <c r="G16" t="n">
+        <v>785</v>
+      </c>
+      <c r="H16" t="n">
+        <v>785</v>
+      </c>
+      <c r="I16" t="n">
+        <v>785</v>
+      </c>
+      <c r="J16" t="n">
+        <v>785</v>
+      </c>
+      <c r="K16" t="n">
+        <v>785</v>
+      </c>
+      <c r="L16" t="n">
+        <v>785</v>
+      </c>
+      <c r="M16" t="n">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>312</v>
+      </c>
+      <c r="C17" t="n">
+        <v>312</v>
+      </c>
+      <c r="D17" t="n">
+        <v>312</v>
+      </c>
+      <c r="E17" t="n">
+        <v>312</v>
+      </c>
+      <c r="F17" t="n">
+        <v>312</v>
+      </c>
+      <c r="G17" t="n">
+        <v>312</v>
+      </c>
+      <c r="H17" t="n">
+        <v>312</v>
+      </c>
+      <c r="I17" t="n">
+        <v>312</v>
+      </c>
+      <c r="J17" t="n">
+        <v>312</v>
+      </c>
+      <c r="K17" t="n">
+        <v>312</v>
+      </c>
+      <c r="L17" t="n">
+        <v>312</v>
+      </c>
+      <c r="M17" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>180</v>
+      </c>
+      <c r="C18" t="n">
+        <v>180</v>
+      </c>
+      <c r="D18" t="n">
+        <v>180</v>
+      </c>
+      <c r="E18" t="n">
+        <v>180</v>
+      </c>
+      <c r="F18" t="n">
+        <v>180</v>
+      </c>
+      <c r="G18" t="n">
+        <v>180</v>
+      </c>
+      <c r="H18" t="n">
+        <v>180</v>
+      </c>
+      <c r="I18" t="n">
+        <v>180</v>
+      </c>
+      <c r="J18" t="n">
+        <v>180</v>
+      </c>
+      <c r="K18" t="n">
+        <v>180</v>
+      </c>
+      <c r="L18" t="n">
+        <v>180</v>
+      </c>
+      <c r="M18" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>76</v>
+      </c>
+      <c r="C19" t="n">
+        <v>76</v>
+      </c>
+      <c r="D19" t="n">
+        <v>76</v>
+      </c>
+      <c r="E19" t="n">
+        <v>76</v>
+      </c>
+      <c r="F19" t="n">
+        <v>76</v>
+      </c>
+      <c r="G19" t="n">
+        <v>76</v>
+      </c>
+      <c r="H19" t="n">
+        <v>76</v>
+      </c>
+      <c r="I19" t="n">
+        <v>76</v>
+      </c>
+      <c r="J19" t="n">
+        <v>76</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76</v>
+      </c>
+      <c r="L19" t="n">
+        <v>76</v>
+      </c>
+      <c r="M19" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>33</v>
+      </c>
+      <c r="E20" t="n">
+        <v>33</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>33</v>
+      </c>
+      <c r="H20" t="n">
+        <v>33</v>
+      </c>
+      <c r="I20" t="n">
+        <v>33</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33</v>
+      </c>
+      <c r="K20" t="n">
+        <v>33</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33</v>
+      </c>
+      <c r="M20" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>162</v>
+      </c>
+      <c r="C21" t="n">
+        <v>162</v>
+      </c>
+      <c r="D21" t="n">
+        <v>162</v>
+      </c>
+      <c r="E21" t="n">
+        <v>162</v>
+      </c>
+      <c r="F21" t="n">
+        <v>162</v>
+      </c>
+      <c r="G21" t="n">
+        <v>162</v>
+      </c>
+      <c r="H21" t="n">
+        <v>162</v>
+      </c>
+      <c r="I21" t="n">
+        <v>162</v>
+      </c>
+      <c r="J21" t="n">
+        <v>162</v>
+      </c>
+      <c r="K21" t="n">
+        <v>162</v>
+      </c>
+      <c r="L21" t="n">
+        <v>162</v>
+      </c>
+      <c r="M21" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>810</v>
+      </c>
+      <c r="C22" t="n">
+        <v>810</v>
+      </c>
+      <c r="D22" t="n">
+        <v>810</v>
+      </c>
+      <c r="E22" t="n">
+        <v>810</v>
+      </c>
+      <c r="F22" t="n">
+        <v>810</v>
+      </c>
+      <c r="G22" t="n">
+        <v>810</v>
+      </c>
+      <c r="H22" t="n">
+        <v>810</v>
+      </c>
+      <c r="I22" t="n">
+        <v>810</v>
+      </c>
+      <c r="J22" t="n">
+        <v>810</v>
+      </c>
+      <c r="K22" t="n">
+        <v>810</v>
+      </c>
+      <c r="L22" t="n">
+        <v>810</v>
+      </c>
+      <c r="M22" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>844</v>
+      </c>
+      <c r="C23" t="n">
+        <v>844</v>
+      </c>
+      <c r="D23" t="n">
+        <v>844</v>
+      </c>
+      <c r="E23" t="n">
+        <v>844</v>
+      </c>
+      <c r="F23" t="n">
+        <v>844</v>
+      </c>
+      <c r="G23" t="n">
+        <v>844</v>
+      </c>
+      <c r="H23" t="n">
+        <v>844</v>
+      </c>
+      <c r="I23" t="n">
+        <v>844</v>
+      </c>
+      <c r="J23" t="n">
+        <v>844</v>
+      </c>
+      <c r="K23" t="n">
+        <v>844</v>
+      </c>
+      <c r="L23" t="n">
+        <v>844</v>
+      </c>
+      <c r="M23" t="n">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>376</v>
+      </c>
+      <c r="C24" t="n">
+        <v>376</v>
+      </c>
+      <c r="D24" t="n">
+        <v>376</v>
+      </c>
+      <c r="E24" t="n">
+        <v>376</v>
+      </c>
+      <c r="F24" t="n">
+        <v>376</v>
+      </c>
+      <c r="G24" t="n">
+        <v>376</v>
+      </c>
+      <c r="H24" t="n">
+        <v>376</v>
+      </c>
+      <c r="I24" t="n">
+        <v>376</v>
+      </c>
+      <c r="J24" t="n">
+        <v>376</v>
+      </c>
+      <c r="K24" t="n">
+        <v>376</v>
+      </c>
+      <c r="L24" t="n">
+        <v>376</v>
+      </c>
+      <c r="M24" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>198</v>
+      </c>
+      <c r="C25" t="n">
+        <v>198</v>
+      </c>
+      <c r="D25" t="n">
+        <v>198</v>
+      </c>
+      <c r="E25" t="n">
+        <v>198</v>
+      </c>
+      <c r="F25" t="n">
+        <v>198</v>
+      </c>
+      <c r="G25" t="n">
+        <v>198</v>
+      </c>
+      <c r="H25" t="n">
+        <v>198</v>
+      </c>
+      <c r="I25" t="n">
+        <v>198</v>
+      </c>
+      <c r="J25" t="n">
+        <v>198</v>
+      </c>
+      <c r="K25" t="n">
+        <v>198</v>
+      </c>
+      <c r="L25" t="n">
+        <v>198</v>
+      </c>
+      <c r="M25" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>70</v>
+      </c>
+      <c r="C26" t="n">
+        <v>70</v>
+      </c>
+      <c r="D26" t="n">
+        <v>70</v>
+      </c>
+      <c r="E26" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" t="n">
+        <v>70</v>
+      </c>
+      <c r="G26" t="n">
+        <v>70</v>
+      </c>
+      <c r="H26" t="n">
+        <v>70</v>
+      </c>
+      <c r="I26" t="n">
+        <v>70</v>
+      </c>
+      <c r="J26" t="n">
+        <v>70</v>
+      </c>
+      <c r="K26" t="n">
+        <v>70</v>
+      </c>
+      <c r="L26" t="n">
+        <v>70</v>
+      </c>
+      <c r="M26" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>817</v>
+      </c>
+      <c r="C27" t="n">
+        <v>817</v>
+      </c>
+      <c r="D27" t="n">
+        <v>817</v>
+      </c>
+      <c r="E27" t="n">
+        <v>817</v>
+      </c>
+      <c r="F27" t="n">
+        <v>817</v>
+      </c>
+      <c r="G27" t="n">
+        <v>817</v>
+      </c>
+      <c r="H27" t="n">
+        <v>817</v>
+      </c>
+      <c r="I27" t="n">
+        <v>817</v>
+      </c>
+      <c r="J27" t="n">
+        <v>817</v>
+      </c>
+      <c r="K27" t="n">
+        <v>817</v>
+      </c>
+      <c r="L27" t="n">
+        <v>817</v>
+      </c>
+      <c r="M27" t="n">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>45</v>
+      </c>
+      <c r="C28" t="n">
+        <v>45</v>
+      </c>
+      <c r="D28" t="n">
+        <v>45</v>
+      </c>
+      <c r="E28" t="n">
+        <v>45</v>
+      </c>
+      <c r="F28" t="n">
+        <v>45</v>
+      </c>
+      <c r="G28" t="n">
+        <v>45</v>
+      </c>
+      <c r="H28" t="n">
+        <v>45</v>
+      </c>
+      <c r="I28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J28" t="n">
+        <v>45</v>
+      </c>
+      <c r="K28" t="n">
+        <v>45</v>
+      </c>
+      <c r="L28" t="n">
+        <v>45</v>
+      </c>
+      <c r="M28" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>182</v>
+      </c>
+      <c r="C29" t="n">
+        <v>182</v>
+      </c>
+      <c r="D29" t="n">
+        <v>182</v>
+      </c>
+      <c r="E29" t="n">
+        <v>182</v>
+      </c>
+      <c r="F29" t="n">
+        <v>182</v>
+      </c>
+      <c r="G29" t="n">
+        <v>182</v>
+      </c>
+      <c r="H29" t="n">
+        <v>182</v>
+      </c>
+      <c r="I29" t="n">
+        <v>182</v>
+      </c>
+      <c r="J29" t="n">
+        <v>182</v>
+      </c>
+      <c r="K29" t="n">
+        <v>182</v>
+      </c>
+      <c r="L29" t="n">
+        <v>182</v>
+      </c>
+      <c r="M29" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>180</v>
+      </c>
+      <c r="C30" t="n">
+        <v>180</v>
+      </c>
+      <c r="D30" t="n">
+        <v>180</v>
+      </c>
+      <c r="E30" t="n">
+        <v>180</v>
+      </c>
+      <c r="F30" t="n">
+        <v>180</v>
+      </c>
+      <c r="G30" t="n">
+        <v>180</v>
+      </c>
+      <c r="H30" t="n">
+        <v>180</v>
+      </c>
+      <c r="I30" t="n">
+        <v>180</v>
+      </c>
+      <c r="J30" t="n">
+        <v>180</v>
+      </c>
+      <c r="K30" t="n">
+        <v>180</v>
+      </c>
+      <c r="L30" t="n">
+        <v>180</v>
+      </c>
+      <c r="M30" t="n">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -988,66 +4213,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1) 10*10 AC-1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2) 10*10 AC-2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3) 10*10 AC-3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4) 20*30 AC-1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5) 20*30 AC-2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6) 20*30 AC-3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7) 10*10 -1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8) 10*10 -2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>9) 10*10 -3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10) 20*30 -1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11) 20*30 -2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12) 20*30 -3</t>
         </is>
@@ -1055,114 +4280,1187 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>42.896</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.566</v>
+        <v>162.982</v>
       </c>
       <c r="C2" t="n">
-        <v>53.914</v>
+        <v>227.137</v>
       </c>
       <c r="D2" t="n">
-        <v>203.844</v>
+        <v>221.425</v>
       </c>
       <c r="E2" t="n">
-        <v>93.524</v>
+        <v>277.844</v>
       </c>
       <c r="F2" t="n">
-        <v>82.58</v>
+        <v>115.245</v>
       </c>
       <c r="G2" t="n">
-        <v>10.24</v>
+        <v>187.464</v>
       </c>
       <c r="H2" t="n">
-        <v>5.348</v>
+        <v>269.118</v>
       </c>
       <c r="I2" t="n">
-        <v>21.785</v>
+        <v>227.852</v>
       </c>
       <c r="J2" t="n">
-        <v>43.685</v>
+        <v>265.541</v>
       </c>
       <c r="K2" t="n">
-        <v>11.359</v>
+        <v>242.977</v>
       </c>
       <c r="L2" t="n">
-        <v>21.458</v>
+        <v>248.972</v>
+      </c>
+      <c r="M2" t="n">
+        <v>317.893</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20.974</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.692</v>
+        <v>78.113</v>
       </c>
       <c r="C3" t="n">
-        <v>18.934</v>
+        <v>82.932</v>
       </c>
       <c r="D3" t="n">
-        <v>196.449</v>
+        <v>118.894</v>
       </c>
       <c r="E3" t="n">
-        <v>95.116</v>
+        <v>223.545</v>
       </c>
       <c r="F3" t="n">
-        <v>79.479</v>
+        <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.753</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>88.36499999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>154.766</v>
+      </c>
       <c r="I3" t="n">
-        <v>-1.202</v>
+        <v>143.15</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.287</v>
+        <v>124.705</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.012</v>
+        <v>161.81</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.871</v>
+        <v>132.332</v>
+      </c>
+      <c r="M3" t="n">
+        <v>95.678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>42.896</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30.566</v>
+      </c>
+      <c r="D4" t="n">
+        <v>53.914</v>
+      </c>
+      <c r="E4" t="n">
+        <v>203.844</v>
+      </c>
+      <c r="F4" t="n">
+        <v>93.524</v>
+      </c>
+      <c r="G4" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.348</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.785</v>
+      </c>
+      <c r="K4" t="n">
+        <v>43.685</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11.359</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21.458</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>20.974</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.692</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.934</v>
+      </c>
+      <c r="E5" t="n">
+        <v>196.449</v>
+      </c>
+      <c r="F5" t="n">
+        <v>95.116</v>
+      </c>
+      <c r="G5" t="n">
+        <v>79.479</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.753</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>-1.202</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.287</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.012</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.871</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>100.102</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C6" t="n">
         <v>64.544</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D6" t="n">
         <v>92.236</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E6" t="n">
         <v>199.12</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F6" t="n">
         <v>110.41</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G6" t="n">
         <v>66.755</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H6" t="n">
         <v>70.133</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I6" t="n">
         <v>74.238</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J6" t="n">
         <v>126.534</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K6" t="n">
         <v>191.862</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
         <v>131.736</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M6" t="n">
         <v>155.355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>275.979</v>
+      </c>
+      <c r="C7" t="n">
+        <v>319.896</v>
+      </c>
+      <c r="D7" t="n">
+        <v>298.002</v>
+      </c>
+      <c r="E7" t="n">
+        <v>182.824</v>
+      </c>
+      <c r="F7" t="n">
+        <v>206.819</v>
+      </c>
+      <c r="G7" t="n">
+        <v>133.736</v>
+      </c>
+      <c r="H7" t="n">
+        <v>448.705</v>
+      </c>
+      <c r="I7" t="n">
+        <v>328.085</v>
+      </c>
+      <c r="J7" t="n">
+        <v>406.981</v>
+      </c>
+      <c r="K7" t="n">
+        <v>369.421</v>
+      </c>
+      <c r="L7" t="n">
+        <v>345.876</v>
+      </c>
+      <c r="M7" t="n">
+        <v>420.143</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-21.185</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-6.595</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75.474</v>
+      </c>
+      <c r="F8" t="n">
+        <v>142.726</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27.618</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.833</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.336</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-4.019</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-34.984</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84.48699999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>54.088</v>
+      </c>
+      <c r="D9" t="n">
+        <v>81.565</v>
+      </c>
+      <c r="E9" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>115.166</v>
+      </c>
+      <c r="G9" t="n">
+        <v>38.539</v>
+      </c>
+      <c r="H9" t="n">
+        <v>147.684</v>
+      </c>
+      <c r="I9" t="n">
+        <v>178.27</v>
+      </c>
+      <c r="J9" t="n">
+        <v>83.497</v>
+      </c>
+      <c r="K9" t="n">
+        <v>170.467</v>
+      </c>
+      <c r="L9" t="n">
+        <v>177.287</v>
+      </c>
+      <c r="M9" t="n">
+        <v>143.364</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.701</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-16.844</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.773</v>
+      </c>
+      <c r="E10" t="n">
+        <v>44.844</v>
+      </c>
+      <c r="F10" t="n">
+        <v>76.65900000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.804</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.198</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7.128</v>
+      </c>
+      <c r="K10" t="n">
+        <v>30.626</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-5.108</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-5.405</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-21.438</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-12.657</v>
+      </c>
+      <c r="E11" t="n">
+        <v>38.702</v>
+      </c>
+      <c r="F11" t="n">
+        <v>64.364</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.044</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.904</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.736</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-4.921</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-6.936</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-9.754</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-9.532</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-23.863</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-16.083</v>
+      </c>
+      <c r="E12" t="n">
+        <v>22.804</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49.407</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.619</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-3.536</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-4.698</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-8.548999999999999</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-16.158</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-25.663</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-11.823</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>41.942</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17.796</v>
+      </c>
+      <c r="D13" t="n">
+        <v>64.708</v>
+      </c>
+      <c r="E13" t="n">
+        <v>29.563</v>
+      </c>
+      <c r="F13" t="n">
+        <v>48.552</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17.814</v>
+      </c>
+      <c r="H13" t="n">
+        <v>43.229</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40.652</v>
+      </c>
+      <c r="J13" t="n">
+        <v>41.792</v>
+      </c>
+      <c r="K13" t="n">
+        <v>111.57</v>
+      </c>
+      <c r="L13" t="n">
+        <v>43.795</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87.98699999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>64.575</v>
+      </c>
+      <c r="D14" t="n">
+        <v>83.10599999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>78.721</v>
+      </c>
+      <c r="F14" t="n">
+        <v>46.59</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="H14" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="I14" t="n">
+        <v>50.809</v>
+      </c>
+      <c r="J14" t="n">
+        <v>39.206</v>
+      </c>
+      <c r="K14" t="n">
+        <v>78.512</v>
+      </c>
+      <c r="L14" t="n">
+        <v>74.53700000000001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>61.752</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>226.852</v>
+      </c>
+      <c r="C15" t="n">
+        <v>248.218</v>
+      </c>
+      <c r="D15" t="n">
+        <v>251.565</v>
+      </c>
+      <c r="E15" t="n">
+        <v>254.756</v>
+      </c>
+      <c r="F15" t="n">
+        <v>101.735</v>
+      </c>
+      <c r="G15" t="n">
+        <v>264.03</v>
+      </c>
+      <c r="H15" t="n">
+        <v>150.226</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>231.678</v>
+      </c>
+      <c r="K15" t="n">
+        <v>211.01</v>
+      </c>
+      <c r="L15" t="n">
+        <v>242.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>249.169</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>330.646</v>
+      </c>
+      <c r="C16" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="D16" t="n">
+        <v>375.577</v>
+      </c>
+      <c r="E16" t="n">
+        <v>432.814</v>
+      </c>
+      <c r="F16" t="n">
+        <v>214.319</v>
+      </c>
+      <c r="G16" t="n">
+        <v>444.521</v>
+      </c>
+      <c r="H16" t="n">
+        <v>361.504</v>
+      </c>
+      <c r="I16" t="n">
+        <v>171.377</v>
+      </c>
+      <c r="J16" t="n">
+        <v>429.552</v>
+      </c>
+      <c r="K16" t="n">
+        <v>377.352</v>
+      </c>
+      <c r="L16" t="n">
+        <v>376.877</v>
+      </c>
+      <c r="M16" t="n">
+        <v>383.425</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>224.168</v>
+      </c>
+      <c r="C17" t="n">
+        <v>205.746</v>
+      </c>
+      <c r="D17" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>421.574</v>
+      </c>
+      <c r="F17" t="n">
+        <v>178.899</v>
+      </c>
+      <c r="G17" t="n">
+        <v>331.002</v>
+      </c>
+      <c r="H17" t="n">
+        <v>335.315</v>
+      </c>
+      <c r="I17" t="n">
+        <v>140.185</v>
+      </c>
+      <c r="J17" t="n">
+        <v>426.081</v>
+      </c>
+      <c r="K17" t="n">
+        <v>282.23</v>
+      </c>
+      <c r="L17" t="n">
+        <v>376.867</v>
+      </c>
+      <c r="M17" t="n">
+        <v>346.912</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="C18" t="n">
+        <v>30.201</v>
+      </c>
+      <c r="D18" t="n">
+        <v>48.346</v>
+      </c>
+      <c r="E18" t="n">
+        <v>398.884</v>
+      </c>
+      <c r="F18" t="n">
+        <v>162.838</v>
+      </c>
+      <c r="G18" t="n">
+        <v>143.292</v>
+      </c>
+      <c r="H18" t="n">
+        <v>32.366</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10.028</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20.694</v>
+      </c>
+      <c r="K18" t="n">
+        <v>35.773</v>
+      </c>
+      <c r="L18" t="n">
+        <v>80.483</v>
+      </c>
+      <c r="M18" t="n">
+        <v>36.838</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>27.223</v>
+      </c>
+      <c r="C19" t="n">
+        <v>12.299</v>
+      </c>
+      <c r="D19" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="E19" t="n">
+        <v>387.557</v>
+      </c>
+      <c r="F19" t="n">
+        <v>154.628</v>
+      </c>
+      <c r="G19" t="n">
+        <v>124.321</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.721</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10.242</v>
+      </c>
+      <c r="M19" t="n">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>135.591</v>
+      </c>
+      <c r="C20" t="n">
+        <v>140.389</v>
+      </c>
+      <c r="D20" t="n">
+        <v>47.214</v>
+      </c>
+      <c r="E20" t="n">
+        <v>225.329</v>
+      </c>
+      <c r="F20" t="n">
+        <v>99.241</v>
+      </c>
+      <c r="G20" t="n">
+        <v>125.58</v>
+      </c>
+      <c r="H20" t="n">
+        <v>101.544</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9.467000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18.955</v>
+      </c>
+      <c r="K20" t="n">
+        <v>104.876</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.176</v>
+      </c>
+      <c r="M20" t="n">
+        <v>38.08</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>158.906</v>
+      </c>
+      <c r="C21" t="n">
+        <v>161.693</v>
+      </c>
+      <c r="D21" t="n">
+        <v>54.319</v>
+      </c>
+      <c r="E21" t="n">
+        <v>215.313</v>
+      </c>
+      <c r="F21" t="n">
+        <v>84.849</v>
+      </c>
+      <c r="G21" t="n">
+        <v>87.883</v>
+      </c>
+      <c r="H21" t="n">
+        <v>315.967</v>
+      </c>
+      <c r="I21" t="n">
+        <v>84.494</v>
+      </c>
+      <c r="J21" t="n">
+        <v>312.499</v>
+      </c>
+      <c r="K21" t="n">
+        <v>218.524</v>
+      </c>
+      <c r="L21" t="n">
+        <v>181.771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-33.176</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>329.713</v>
+      </c>
+      <c r="C22" t="n">
+        <v>349.106</v>
+      </c>
+      <c r="D22" t="n">
+        <v>360.588</v>
+      </c>
+      <c r="E22" t="n">
+        <v>293.602</v>
+      </c>
+      <c r="F22" t="n">
+        <v>115.539</v>
+      </c>
+      <c r="G22" t="n">
+        <v>148.508</v>
+      </c>
+      <c r="H22" t="n">
+        <v>351.305</v>
+      </c>
+      <c r="I22" t="n">
+        <v>218.601</v>
+      </c>
+      <c r="J22" t="n">
+        <v>447.263</v>
+      </c>
+      <c r="K22" t="n">
+        <v>245.673</v>
+      </c>
+      <c r="L22" t="n">
+        <v>356.592</v>
+      </c>
+      <c r="M22" t="n">
+        <v>378.77</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>68.547</v>
+      </c>
+      <c r="C23" t="n">
+        <v>31.235</v>
+      </c>
+      <c r="D23" t="n">
+        <v>33.852</v>
+      </c>
+      <c r="E23" t="n">
+        <v>26.795</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="G23" t="n">
+        <v>149.885</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21.522</v>
+      </c>
+      <c r="I23" t="n">
+        <v>26.488</v>
+      </c>
+      <c r="J23" t="n">
+        <v>56.446</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20.712</v>
+      </c>
+      <c r="L23" t="n">
+        <v>32.653</v>
+      </c>
+      <c r="M23" t="n">
+        <v>35.369</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>16.163</v>
+      </c>
+      <c r="C24" t="n">
+        <v>26.155</v>
+      </c>
+      <c r="D24" t="n">
+        <v>22.878</v>
+      </c>
+      <c r="E24" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.766</v>
+      </c>
+      <c r="G24" t="n">
+        <v>126.464</v>
+      </c>
+      <c r="H24" t="n">
+        <v>20.425</v>
+      </c>
+      <c r="I24" t="n">
+        <v>25.756</v>
+      </c>
+      <c r="J24" t="n">
+        <v>47.703</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20.024</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30.576</v>
+      </c>
+      <c r="M24" t="n">
+        <v>30.786</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>13.675</v>
+      </c>
+      <c r="C25" t="n">
+        <v>17.848</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="E25" t="n">
+        <v>27.029</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.027</v>
+      </c>
+      <c r="G25" t="n">
+        <v>98.07899999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>19.045</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.804</v>
+      </c>
+      <c r="J25" t="n">
+        <v>25.778</v>
+      </c>
+      <c r="K25" t="n">
+        <v>23.603</v>
+      </c>
+      <c r="L25" t="n">
+        <v>27.658</v>
+      </c>
+      <c r="M25" t="n">
+        <v>18.936</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8.202</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11.272</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="E26" t="n">
+        <v>23.438</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11.379</v>
+      </c>
+      <c r="G26" t="n">
+        <v>96.486</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.428</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.246</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.861</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>23.043</v>
+      </c>
+      <c r="C27" t="n">
+        <v>40.443</v>
+      </c>
+      <c r="D27" t="n">
+        <v>35.241</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26.753</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.309</v>
+      </c>
+      <c r="G27" t="n">
+        <v>141.554</v>
+      </c>
+      <c r="H27" t="n">
+        <v>33.252</v>
+      </c>
+      <c r="I27" t="n">
+        <v>18.642</v>
+      </c>
+      <c r="J27" t="n">
+        <v>58.309</v>
+      </c>
+      <c r="K27" t="n">
+        <v>37.326</v>
+      </c>
+      <c r="L27" t="n">
+        <v>43.613</v>
+      </c>
+      <c r="M27" t="n">
+        <v>36.754</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.508</v>
+      </c>
+      <c r="E28" t="n">
+        <v>22.764</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11.133</v>
+      </c>
+      <c r="G28" t="n">
+        <v>68.72799999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.231</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.365</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.884</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4.509</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5.785</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.696</v>
+      </c>
+      <c r="E29" t="n">
+        <v>22.459</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.927</v>
+      </c>
+      <c r="G29" t="n">
+        <v>75.494</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.992</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.339</v>
+      </c>
+      <c r="J29" t="n">
+        <v>16.438</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11.718</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.617</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.428</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-2.192</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13.844</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.942</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-3.513</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-3.786</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.703</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-2.038</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-2.707</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-2.543</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-3.694</v>
       </c>
     </row>
   </sheetData>
@@ -1176,66 +5474,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1) 10*10 AC-1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2) 10*10 AC-2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3) 10*10 AC-3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4) 20*30 AC-1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5) 20*30 AC-2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6) 20*30 AC-3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7) 10*10 -1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8) 10*10 -2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>9) 10*10 -3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10) 20*30 -1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11) 20*30 -2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12) 20*30 -3</t>
         </is>
@@ -1243,114 +5541,1187 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.840066816e-06</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.34280356e-07</v>
+        <v>2.6563132324e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.906719396000001e-06</v>
+        <v>5.1591216769e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1552376336e-05</v>
+        <v>4.902903062500001e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>8.746738576e-06</v>
+        <v>7.7197288336e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8194564e-06</v>
+        <v>1.3281410025e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.048576e-07</v>
+        <v>3.5142751296e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.860110399999999e-08</v>
+        <v>7.242449792399997e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>4.745862249999999e-07</v>
+        <v>5.1916533904e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.908379225e-06</v>
+        <v>7.051202268099999e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.29026881e-07</v>
+        <v>5.9037822529e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>4.604457639999999e-07</v>
+        <v>6.1987056784e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.000101055959449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.39908676e-07</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5.9166864e-08</v>
+        <v>6.101640769e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>3.58496356e-07</v>
+        <v>6.877716624000001e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8592209601e-05</v>
+        <v>1.4135783236e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>9.047053456000001e-06</v>
+        <v>4.9972367025e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.316911440999999e-06</v>
+        <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.297328999999999e-09</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>7.808373225e-06</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.3952514756e-05</v>
+      </c>
       <c r="I3" t="n">
-        <v>3.549455999999999e-09</v>
+        <v>2.04919225e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.719201e-09</v>
+        <v>1.5551337025e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.374569e-09</v>
+        <v>2.61824761e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>3.717184e-09</v>
+        <v>1.7511758224e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.154279684e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.840066816e-06</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9.34280356e-07</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.906719396000001e-06</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.1552376336e-05</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.746738576e-06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.8194564e-06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.048576e-07</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.860110399999999e-08</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.745862249999999e-07</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.908379225e-06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.29026881e-07</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.604457639999999e-07</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4.39908676e-07</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.9166864e-08</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.58496356e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.8592209601e-05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.047053456000001e-06</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.316911440999999e-06</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.297328999999999e-09</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>3.549455999999999e-09</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.719201e-09</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.374569e-09</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.717184e-09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>1.0020410404e-05</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C6" t="n">
         <v>4.165927935999999e-06</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D6" t="n">
         <v>8.507479695999999e-06</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E6" t="n">
         <v>3.964877439999999e-05</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F6" t="n">
         <v>1.21903681e-05</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G6" t="n">
         <v>4.456230025e-06</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H6" t="n">
         <v>4.918637689e-06</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I6" t="n">
         <v>5.511280644e-06</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J6" t="n">
         <v>1.6010853156e-05</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K6" t="n">
         <v>3.6811027044e-05</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
         <v>1.7354373696e-05</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M6" t="n">
         <v>2.4135176025e-05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5388136147e-05</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.4111150272e-05</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.9601730668e-05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.114153832533334e-05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.425803292033333e-05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.961772565333333e-06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.711205900833333e-05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.587992240833332e-05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.521117812033333e-05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.549062508033333e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.987673579199999e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.884004681633333e-05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8.3814025e-08</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8.253554409999998e-07</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.10221001e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.696324676e-06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.0370711076e-05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.62753924e-07</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.020644e-09</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.622500000000001e-09</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.632836e-09</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.803248896e-06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.55077209e-07</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.625742564e-06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2.379351056333333e-06</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9.751705813333334e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.217616408333333e-06</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.991763333333333e-06</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.421069185333333e-06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.950848403333335e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.270187952000001e-06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.059339763333333e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.323916336333334e-06</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.686332696333333e-06</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.047689345633333e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.851078831999999e-06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>6.147213333333333e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.649860083333333e-07</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.02878208e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.703281120000001e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.958867427e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.583680533333334e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.423816333333334e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.179840133333333e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.879498700000001e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.126506253333333e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.823471413333334e-07</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.02163888e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8.4333612e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.584480083333333e-07</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.154192213333333e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.992816013333333e-07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.380908165333333e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.211226133333333e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.505462533333333e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.128488033333333e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.486464533333332e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.301252083333333e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.588539069999999e-07</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.723483519999999e-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.10098092e-07</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.536808563333333e-07</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.132216333333333e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.733408053333333e-07</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8.13683883e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.1001675e-08</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.609234700000002e-08</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.31791152e-07</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.058507500000001e-08</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.184760333333333e-07</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.030879053333334e-07</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.77777612e-07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5.863771213333333e-07</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.137008e-07</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.395708421333333e-06</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.913236563333333e-07</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.85765568e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.05779532e-07</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.229154803333332e-07</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.508617013333334e-07</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.821904213333334e-07</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.149288299999999e-06</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.393340083333334e-07</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.2334267e-08</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.580570723e-06</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.389976875e-06</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.302202412e-06</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.065665280333333e-06</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.235427000000001e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.366598533333332e-08</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.651584033333333e-06</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.605181603333334e-07</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.123701453333335e-07</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.054711381333333e-06</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.851921456333334e-06</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.271103168e-06</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5.1461829904e-05</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.161217552399999e-05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.328494922499999e-05</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.490061953599998e-05</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.0350010225e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.971184089999999e-05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.2567851076e-05</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>5.3674695684e-05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.45252201e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.86559961e-05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6.2085190561e-05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.644225910533333e-05</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.667022413333334e-05</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.701936097633333e-05</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.244265286533334e-05</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.531087792033333e-05</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.586630648033334e-05</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.356171400533333e-05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.790025376333333e-06</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.150497356800002e-05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.746484396799999e-05</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.734542437633334e-05</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.900491020833333e-05</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.675043074133334e-05</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.4110472172e-05</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.381408333333334e-05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5.924154582533333e-05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.0668284067e-05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.6520774668e-05</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.747871640833333e-05</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.550611408333334e-06</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.051500618700001e-05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.655125763333334e-05</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.734291189633333e-05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.011597858133333e-05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8.164200333333334e-07</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.04033467e-07</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.791119053333331e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.303614848533333e-05</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.838738081333331e-06</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.844199088000001e-06</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.491859853333333e-07</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.777549653333334e-07</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.42747212e-07</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.265691763333335e-07</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.159171096333333e-06</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.523460813333334e-07</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2.470305763333333e-07</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.042180033333333e-08</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.984021333333334e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.006680941633335e-05</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.969939461333333e-06</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.151903680333333e-06</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.97754483e-07</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.67227532e-07</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.474062803333333e-07</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.57513548e-07</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.857827213333332e-07</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.3975787e-08</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>6.128306427000002e-06</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6.569690440333335e-06</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7.430539319999999e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.692438608033334e-05</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.282925360333333e-06</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.2567788e-06</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.437061312e-06</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.55911088e-07</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.197640083333333e-07</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.666325125333334e-06</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.861213633333334e-08</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7.745418720000001e-07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8.417038945333335e-06</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8.714875416333335e-06</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9.835179203333333e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.545322932299999e-05</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.399784267000001e-06</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.574473896333333e-06</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.327838169633334e-05</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.379745345333333e-06</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.255187500033334e-05</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.591757952533333e-05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.101356548033333e-05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7.854095603333332e-07</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.623688745633334e-05</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4.062499974533333e-05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.334123524800001e-05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.873404480133333e-05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.449753507e-06</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.351542021333333e-06</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.113840100833334e-05</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.5928799067e-05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.668139705633332e-05</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.0118407643e-05</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4.238595148799999e-05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.782223763333333e-05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4.698691208999999e-05</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9.756252249999999e-06</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.145957904e-05</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.179720250000001e-06</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.147041e-06</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.2465513225e-05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.63196484e-06</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.016141440000001e-06</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.186150915999999e-05</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.28986944e-06</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.066218409e-05</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.250966161e-05</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2.61242569e-06</v>
+      </c>
+      <c r="C24" t="n">
+        <v>6.840840250000001e-06</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.23402884e-06</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.890624999999999e-06</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.15906756e-06</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.5993143296e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.171806250000001e-06</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6.633715360000001e-06</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.275576209e-05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.00960576e-06</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9.34891776e-06</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9.477777960000001e-06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1.87005625e-06</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.18551104e-06</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.134521e-06</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.305668410000001e-06</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.44648729e-06</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.619490240999999e-06</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.627120250000001e-06</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.39334416e-06</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6.645052839999999e-06</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.571016090000001e-06</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7.64964964e-06</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.58572096e-06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>6.727280399999999e-07</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.27057984e-06</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.802851600000001e-07</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.49339844e-06</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.29481641e-06</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9.309548195999999e-06</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.3995081e-07</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.430480999999999e-08</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.26025e-07</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.1196816e-07</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3.901251600000001e-07</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.790024099999999e-07</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5.309798490000001e-06</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.635636249e-05</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.241928081e-05</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.15723009e-06</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.77129481e-06</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.003753491600001e-05</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.105695504e-05</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.47524164e-06</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.399939481e-05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.393230276e-05</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.902093769e-05</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.350856516e-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6.548481000000001e-08</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.982464e-08</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.019241e-08</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.18199696e-06</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.23943689e-06</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.723537983999999e-06</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.9254544e-07</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.600225e-08</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.3329801e-07</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.1196816e-07</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.1937025e-07</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.2398864e-07</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2.0331081e-07</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.3466225e-07</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.3660416e-07</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.04406681e-06</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.19399329e-06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.699344036000001e-06</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.5904064e-07</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.3860921e-07</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.70207844e-06</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.37311524e-06</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.67294689e-06</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.946318399999999e-07</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.492809999999999e-09</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5.3361e-08</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8.952063999999999e-08</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.91656336e-06</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.5307364e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.175784099999998e-08</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.6736281e-07</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.921000000000002e-09</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.276209e-08</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8.898288999999999e-08</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.873635999999999e-08</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.4691889e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1364,66 +6735,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1) 10*10 AC-1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2) 10*10 AC-2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3) 10*10 AC-3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4) 20*30 AC-1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5) 20*30 AC-2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6) 20*30 AC-3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7) 10*10 -1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8) 10*10 -2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>9) 10*10 -3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10) 20*30 -1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11) 20*30 -2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12) 20*30 -3</t>
         </is>
@@ -1431,114 +6802,1187 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.273264</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.309028</v>
+        <v>0.339931</v>
       </c>
       <c r="C2" t="n">
-        <v>0.266319</v>
+        <v>0.326389</v>
       </c>
       <c r="D2" t="n">
-        <v>0.284375</v>
+        <v>0.293403</v>
       </c>
       <c r="E2" t="n">
-        <v>3.969444</v>
+        <v>1.155903</v>
       </c>
       <c r="F2" t="n">
-        <v>2.269444</v>
+        <v>1.167361</v>
       </c>
       <c r="G2" t="n">
-        <v>0.148264</v>
+        <v>0.424306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.051042</v>
+        <v>0.357292</v>
       </c>
       <c r="I2" t="n">
-        <v>0.19375</v>
+        <v>0.236458</v>
       </c>
       <c r="J2" t="n">
-        <v>0.210417</v>
+        <v>0.21875</v>
       </c>
       <c r="K2" t="n">
-        <v>0.204514</v>
+        <v>0.293056</v>
       </c>
       <c r="L2" t="n">
-        <v>0.202083</v>
+        <v>0.327083</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.269444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.302083</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.334028</v>
+        <v>0.185069</v>
       </c>
       <c r="C3" t="n">
-        <v>0.299306</v>
+        <v>0.19375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000694</v>
+        <v>0.232639</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000694</v>
+        <v>0.281597</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000347</v>
+        <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000347</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>0.249306</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.165972</v>
+      </c>
       <c r="I3" t="n">
-        <v>0.092708</v>
+        <v>0.160417</v>
       </c>
       <c r="J3" t="n">
-        <v>0.057292</v>
+        <v>0.181597</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1</v>
+        <v>0.192014</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08541700000000001</v>
+        <v>0.166667</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.160764</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.273264</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.309028</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.266319</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.284375</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.969444</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.269444</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.148264</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.051042</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.210417</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.204514</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.202083</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.302083</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.334028</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.299306</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.000694</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.000694</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.092708</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.057292</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.08541700000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>0.354861</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C6" t="n">
         <v>0.338542</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D6" t="n">
         <v>0.359722</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E6" t="n">
         <v>0.530903</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F6" t="n">
         <v>1.026042</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G6" t="n">
         <v>0.511111</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H6" t="n">
         <v>0.583681</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I6" t="n">
         <v>0.499653</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J6" t="n">
         <v>0.290278</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K6" t="n">
         <v>0.485069</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
         <v>0.459375</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M6" t="n">
         <v>0.445833</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.614931</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.717014</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.056597</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.037153</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.564236</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.080556</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.047569</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.061806</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.08784699999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.233681</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.166667</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.263889</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.111111</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.350694</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.288194</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.038194</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.100694</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.152778</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.052083</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.460417</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.405903</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.522917</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.05625</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.008681</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.652083</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.584375</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.482986</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.445139</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.328819</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.550347</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.522917</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.335417</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.454167</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.407639</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.511806</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.339236</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.590625</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.214583</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.127083</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.219792</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.13125</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.226042</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.397569</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.324306</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.306944</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.369444</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.224653</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.417361</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.170833</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.125694</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.124653</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.097569</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.095139</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.121875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.515972</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.437153</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.505903</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.133681</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.338194</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.376736</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.369444</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.195139</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.362153</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.130903</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.268403</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.488889</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.547917</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.940625</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.631944</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.570833</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.757986</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.353819</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.703472</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.500347</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.563542</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.429514</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16.673958</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.381944</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.553472</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.487153</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.094444</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.148958</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.16875</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.01875</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.9125</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.104167</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9246529999999999</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.176736</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.120833</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.286111</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.296181</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.289583</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.756944</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.306944</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.046528</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.133333</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.150347</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.156597</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.396875</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.327778</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.661458</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.21875</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.124653</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9708329999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.076389</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.060764</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.07256899999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.154514</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.317361</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.132986</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.270139</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.257639</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.330208</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.405903</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.101042</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.251389</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.130556</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.205208</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.100694</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.144444</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.174306</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.198611</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.137847</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.238889</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.210069</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.141319</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.474653</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.092361</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.073958</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.064236</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.088542</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.053125</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.061458</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.265972</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.452778</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.219444</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.445486</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.044792</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.271528</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.092014</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.100347</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.093056</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.052431</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.067708</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.000694</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.000694</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.000694</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005903</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.491319</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.026736</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.000347</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.197222</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.197917</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.251042</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.303472</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.139236</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.221181</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.146875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.169444</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.101042</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.126736</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.034028</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.319792</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.439583</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.469792</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.582639</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.472222</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.052431</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.021181</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.073958</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.118403</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.164931</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.238542</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.028819</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.163194</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.210764</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.805903</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.795833</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.788194</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.033681</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.022222</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.117708</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.031944</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.042014</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.045486</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.190625</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.169097</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.185764</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.272222</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.982639</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.024306</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.017361</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.030556</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.025347</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.036111</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.164931</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.147569</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.151736</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.003125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.106597</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.436806</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.043403</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.092014</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.054167</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.080208</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.115625</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.103472</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.001042</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.132292</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.154167</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.001042</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.160417</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.08472200000000001</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.130903</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.104167</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.072917</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.089931</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.101736</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.202431</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.328125</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.831597</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.504861</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.07083299999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.015278</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.067014</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.057639</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.043403</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.057639</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.052431</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.105208</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.410764</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.028819</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.040625</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.270139</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.136458</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.272569</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.017014</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.157639</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.144792</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.139583</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.227083</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.212153</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.347569</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.092708</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.093056</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.058333</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.08819399999999999</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.077431</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.117708</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.270486</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.378125</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.493403</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.389236</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.026736</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.320486</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.129861</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.863542</v>
       </c>
     </row>
   </sheetData>

--- a/mfc_analysis.xlsx
+++ b/mfc_analysis.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>29/07/2024</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -578,7 +578,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -621,7 +621,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -664,7 +664,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -707,7 +707,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -750,7 +750,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -793,7 +793,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -836,7 +836,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -879,7 +879,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -922,7 +922,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1008,7 +1008,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1051,7 +1051,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1094,7 +1094,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1137,7 +1137,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/02/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1180,7 +1180,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1223,7 +1223,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1266,7 +1266,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1309,7 +1309,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1352,7 +1352,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1395,7 +1395,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1438,7 +1438,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1481,7 +1481,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1524,7 +1524,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1567,7 +1567,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1610,7 +1610,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1653,7 +1653,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1696,7 +1696,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>18/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1820,7 +1820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1863,7 +1863,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>29/07/2024</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1906,7 +1906,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1949,7 +1949,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1992,7 +1992,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2035,7 +2035,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2078,7 +2078,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2121,7 +2121,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2164,7 +2164,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2207,7 +2207,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2250,7 +2250,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2293,7 +2293,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2336,7 +2336,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2379,7 +2379,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2422,7 +2422,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2465,7 +2465,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/02/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2508,7 +2508,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2551,7 +2551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2594,7 +2594,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2637,7 +2637,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2680,7 +2680,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2723,7 +2723,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2766,7 +2766,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2809,7 +2809,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2895,7 +2895,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2938,7 +2938,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2981,7 +2981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3024,7 +3024,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>18/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3148,7 +3148,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3191,7 +3191,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>29/07/2024</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -3234,7 +3234,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3277,7 +3277,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3318,7 +3318,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -3361,7 +3361,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3404,7 +3404,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3447,7 +3447,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3490,7 +3490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3533,7 +3533,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3576,7 +3576,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3619,7 +3619,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -3662,7 +3662,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3705,7 +3705,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3746,7 +3746,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -3789,7 +3789,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/02/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -3832,7 +3832,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3875,7 +3875,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3918,7 +3918,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3961,7 +3961,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -4004,7 +4004,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4047,7 +4047,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -4090,7 +4090,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4133,7 +4133,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4176,7 +4176,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4219,7 +4219,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4262,7 +4262,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4305,7 +4305,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4348,7 +4348,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>18/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4472,7 +4472,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4515,7 +4515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>29/07/2024</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4558,7 +4558,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4601,7 +4601,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4642,7 +4642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4685,7 +4685,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4728,7 +4728,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4771,7 +4771,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4814,7 +4814,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4857,7 +4857,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4900,7 +4900,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4943,7 +4943,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4986,7 +4986,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5029,7 +5029,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5070,7 +5070,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5113,7 +5113,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/02/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5156,7 +5156,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5199,7 +5199,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5242,7 +5242,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5285,7 +5285,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5328,7 +5328,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5371,7 +5371,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5414,7 +5414,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5457,7 +5457,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5500,7 +5500,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5543,7 +5543,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5586,7 +5586,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -5629,7 +5629,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -5672,7 +5672,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>18/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -5796,7 +5796,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5839,7 +5839,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>29/07/2024</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5882,7 +5882,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5925,7 +5925,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5966,7 +5966,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6009,7 +6009,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6052,7 +6052,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6095,7 +6095,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6138,7 +6138,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6181,7 +6181,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6224,7 +6224,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6267,7 +6267,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6310,7 +6310,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6353,7 +6353,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6394,7 +6394,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6437,7 +6437,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/02/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6480,7 +6480,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6523,7 +6523,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6566,7 +6566,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6609,7 +6609,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6652,7 +6652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6695,7 +6695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6738,7 +6738,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6781,7 +6781,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6824,7 +6824,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6867,7 +6867,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6910,7 +6910,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6953,7 +6953,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6996,7 +6996,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>18/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7120,7 +7120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -7163,7 +7163,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>29/07/2024</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7206,7 +7206,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7247,7 +7247,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7288,7 +7288,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7331,7 +7331,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7374,7 +7374,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7415,7 +7415,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7458,7 +7458,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7501,7 +7501,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -7544,7 +7544,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -7587,7 +7587,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7630,7 +7630,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -7673,7 +7673,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7714,7 +7714,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -7757,7 +7757,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/02/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -7800,7 +7800,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7843,7 +7843,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -7886,7 +7886,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -7929,7 +7929,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7972,7 +7972,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -8015,7 +8015,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -8058,7 +8058,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -8101,7 +8101,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -8144,7 +8144,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -8187,7 +8187,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -8230,7 +8230,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -8271,7 +8271,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -8314,7 +8314,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>18/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -8438,7 +8438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -8481,7 +8481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>29/07/2024</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -8524,7 +8524,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -8567,7 +8567,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -8610,7 +8610,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -8653,7 +8653,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -8696,7 +8696,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -8739,7 +8739,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -8782,7 +8782,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -8825,7 +8825,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -8868,7 +8868,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -8911,7 +8911,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -8954,7 +8954,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -8997,7 +8997,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -9040,7 +9040,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -9083,7 +9083,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/02/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -9126,7 +9126,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -9169,7 +9169,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -9212,7 +9212,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -9255,7 +9255,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -9298,7 +9298,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -9341,7 +9341,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -9384,7 +9384,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -9427,7 +9427,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -9470,7 +9470,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -9513,7 +9513,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -9556,7 +9556,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -9599,7 +9599,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -9642,7 +9642,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>18/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
